--- a/CARTERA_acc_etf_fon.xlsx
+++ b/CARTERA_acc_etf_fon.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="120" yWindow="105" windowWidth="28515" windowHeight="14385"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="CARTERA" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>

--- a/CARTERA_acc_etf_fon.xlsx
+++ b/CARTERA_acc_etf_fon.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="CARTERA" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId2"/>
   </externalReferences>
   <calcPr calcId="144525"/>
 </workbook>
@@ -2531,22 +2529,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>